--- a/financials/Revii_VoiceCare_Financial_Model.xlsx
+++ b/financials/Revii_VoiceCare_Financial_Model.xlsx
@@ -238,7 +238,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -265,11 +265,25 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -505,6 +519,16 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="26" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="26" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -579,6 +603,328 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!B55</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FCFCFB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$C$54:$G$54</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$C$55:$G$55</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Dashboard'!B56</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="EB6834"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
+              <a:solidFill>
+                <a:srgbClr val="FCFCFB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Dashboard'!$C$54:$G$54</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Dashboard'!$C$56:$G$56</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <overlap val="-10"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:solidFill>
+              <a:srgbClr val="E8E8E4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E8E8E4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:solidFill>
+              <a:srgbClr val="E8E8E4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'P&amp;L Monthly'!B63</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'P&amp;L Monthly'!$D$4:$BK$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'P&amp;L Monthly'!$C$63:$BK$63</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'P&amp;L Monthly'!B60</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'P&amp;L Monthly'!$D$4:$BK$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'P&amp;L Monthly'!$C$60:$BK$60</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:solidFill>
+              <a:srgbClr val="E8E8E4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="6"/>
+        <tickMarkSkip val="6"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E8E8E4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+            <a:solidFill>
+              <a:srgbClr val="E8E8E4"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6840000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6840000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1236,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J69"/>
+  <dimension ref="B2:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1549,12 +1895,17 @@
       </c>
       <c r="E28" s="83" t="inlineStr">
         <is>
-          <t>Spain Y1</t>
+          <t>Spain Y2</t>
         </is>
       </c>
       <c r="F28" s="83" t="inlineStr">
         <is>
           <t>Spain Y5</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>Portugal Y1 and Spain Y2 are each market's first trading year — Spain launches in month 17, so it has no Year 1.</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1924,7 @@
         <v/>
       </c>
       <c r="E29" s="84">
-        <f>IFERROR(SUM('Model ES'!D24:O25)/SUM('Model ES'!D14:O14),0)</f>
+        <f>IFERROR(SUM('Model ES'!P24:AA25)/SUM('Model ES'!P14:AA14),0)</f>
         <v/>
       </c>
       <c r="F29" s="84">
@@ -1601,7 +1952,7 @@
         <v/>
       </c>
       <c r="E30" s="84">
-        <f>IFERROR(SUM('Model ES'!D34:O34)/SUM('Model ES'!D14:O14),0)</f>
+        <f>IFERROR(SUM('Model ES'!P34:AA34)/SUM('Model ES'!P14:AA14),0)</f>
         <v/>
       </c>
       <c r="F30" s="84">
@@ -1658,23 +2009,23 @@
     <row r="33">
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Average customer life (months)</t>
-        </is>
-      </c>
-      <c r="C33" s="86">
-        <f>Inputs!$C$43</f>
-        <v/>
-      </c>
-      <c r="D33" s="86">
-        <f>Inputs!$C$43</f>
-        <v/>
-      </c>
-      <c r="E33" s="86">
-        <f>Inputs!$D$43</f>
-        <v/>
-      </c>
-      <c r="F33" s="86">
-        <f>Inputs!$D$43</f>
+          <t>Average customer life (months, capped for LTV)</t>
+        </is>
+      </c>
+      <c r="C33" s="113">
+        <f>MIN(Inputs!$C$43,Inputs!$C$105)</f>
+        <v/>
+      </c>
+      <c r="D33" s="113">
+        <f>MIN(Inputs!$C$43,Inputs!$C$105)</f>
+        <v/>
+      </c>
+      <c r="E33" s="113">
+        <f>MIN(Inputs!$D$43,Inputs!$C$105)</f>
+        <v/>
+      </c>
+      <c r="F33" s="113">
+        <f>MIN(Inputs!$D$43,Inputs!$C$105)</f>
         <v/>
       </c>
     </row>
@@ -1700,11 +2051,7 @@
         <f>F31*F33</f>
         <v/>
       </c>
-      <c r="J34" s="14" t="inlineStr">
-        <is>
-          <t>A LTV/COCA above 3.0x is the usual threshold for a healthy subscription business.</t>
-        </is>
-      </c>
+      <c r="J34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="11" t="inlineStr">
@@ -1751,6 +2098,11 @@
         <f>IFERROR(F34/F35,0)</f>
         <v/>
       </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>A LTV/COCA above 3.0x is the usual threshold for a healthy subscription business. A negative figure means the customer loses money over their life at these assumptions.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="11" t="inlineStr">
@@ -1758,20 +2110,20 @@
           <t>Months to pay back the acquisition cost</t>
         </is>
       </c>
-      <c r="C37" s="86">
-        <f>IFERROR(C35/C31,0)</f>
-        <v/>
-      </c>
-      <c r="D37" s="86">
-        <f>IFERROR(D35/D31,0)</f>
-        <v/>
-      </c>
-      <c r="E37" s="86">
-        <f>IFERROR(E35/E31,0)</f>
-        <v/>
-      </c>
-      <c r="F37" s="86">
-        <f>IFERROR(F35/F31,0)</f>
+      <c r="C37" s="113">
+        <f>IF(C31&lt;=0,"never",C35/C31)</f>
+        <v/>
+      </c>
+      <c r="D37" s="113">
+        <f>IF(D31&lt;=0,"never",D35/D31)</f>
+        <v/>
+      </c>
+      <c r="E37" s="113">
+        <f>IF(E31&lt;=0,"never",E35/E31)</f>
+        <v/>
+      </c>
+      <c r="F37" s="113">
+        <f>IF(F31&lt;=0,"never",F35/F31)</f>
         <v/>
       </c>
     </row>
@@ -1943,6 +2295,11 @@
         <f>IFERROR(C48/C43,0)</f>
         <v/>
       </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>The money multiple and IRR are driven almost entirely by the exit multiple on Inputs!C103. Treat them as a framing device, not a forecast.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="77" t="inlineStr">
@@ -2290,6 +2647,34 @@
       <c r="C69" s="14" t="inlineStr">
         <is>
           <t>Receivables and payables use days ratios; VAT settlement timing is ignored. Fine for sizing, not for a cash-management calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>The bars share one axis because both series are euros. Year 1 is short — it contains the build months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="116" t="inlineStr">
+        <is>
+          <t>NET REVENUE AND EBITDA BY YEAR  (EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Both series are euros on one axis. The blue line is money the founders have put in; the orange line is what the business has generated. Where orange crosses blue, the venture has repaid itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="116" t="inlineStr">
+        <is>
+          <t>CUMULATIVE FOUNDERS' EQUITY IN vs CUMULATIVE FREE CASH FLOW  (EUR, by month)</t>
         </is>
       </c>
     </row>
@@ -2303,6 +2688,7 @@
     <mergeCell ref="C67:H67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2345,22 +2731,22 @@
           <t>Lever</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="93" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="93" t="inlineStr">
         <is>
           <t>1 Conservative</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="93" t="inlineStr">
         <is>
           <t>2 Base</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="93" t="inlineStr">
         <is>
           <t>3 Optimistic</t>
         </is>
@@ -2637,12 +3023,12 @@
           <t>Active scenario</t>
         </is>
       </c>
-      <c r="C17" s="20">
-        <f>Inputs!C6</f>
+      <c r="C17" s="114">
+        <f>Inputs!C7</f>
         <v/>
       </c>
       <c r="D17" s="21">
-        <f>INDEX($D$5:$F$5,1,Inputs!C6)</f>
+        <f>INDEX($D$5:$F$5,1,Inputs!C7)</f>
         <v/>
       </c>
     </row>
@@ -2664,7 +3050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I106"/>
+  <dimension ref="B2:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2773,7 +3159,7 @@
           <t>Product build period before launch (months)</t>
         </is>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="115" t="n">
         <v>4</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -2858,12 +3244,12 @@
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="83" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="83" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -2913,10 +3299,10 @@
           <t>Prices include VAT?  (1 = yes, 0 = no)</t>
         </is>
       </c>
-      <c r="C22" s="30" t="n">
+      <c r="C22" s="115" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="30" t="n">
+      <c r="D22" s="115" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="14" t="inlineStr">
@@ -3050,12 +3436,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C31" s="83" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D31" s="34" t="inlineStr">
+      <c r="D31" s="83" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
@@ -3301,27 +3687,27 @@
           <t>Years since that market launched</t>
         </is>
       </c>
-      <c r="C48" s="34" t="inlineStr">
+      <c r="C48" s="83" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D48" s="83" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E48" s="34" t="inlineStr">
+      <c r="E48" s="83" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F48" s="34" t="inlineStr">
+      <c r="F48" s="83" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G48" s="34" t="inlineStr">
+      <c r="G48" s="83" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
@@ -3498,27 +3884,27 @@
           <t>Model year</t>
         </is>
       </c>
-      <c r="C60" s="34" t="inlineStr">
+      <c r="C60" s="83" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D60" s="34" t="inlineStr">
+      <c r="D60" s="83" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E60" s="34" t="inlineStr">
+      <c r="E60" s="83" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F60" s="34" t="inlineStr">
+      <c r="F60" s="83" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G60" s="34" t="inlineStr">
+      <c r="G60" s="83" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
@@ -3616,27 +4002,27 @@
           <t>Years since that market launched</t>
         </is>
       </c>
-      <c r="C67" s="34" t="inlineStr">
+      <c r="C67" s="83" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D67" s="34" t="inlineStr">
+      <c r="D67" s="83" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E67" s="34" t="inlineStr">
+      <c r="E67" s="83" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F67" s="34" t="inlineStr">
+      <c r="F67" s="83" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G67" s="34" t="inlineStr">
+      <c r="G67" s="83" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
@@ -3725,27 +4111,27 @@
           <t>Model year</t>
         </is>
       </c>
-      <c r="C73" s="34" t="inlineStr">
+      <c r="C73" s="83" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D73" s="34" t="inlineStr">
+      <c r="D73" s="83" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E73" s="34" t="inlineStr">
+      <c r="E73" s="83" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F73" s="34" t="inlineStr">
+      <c r="F73" s="83" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G73" s="34" t="inlineStr">
+      <c r="G73" s="83" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
@@ -4272,8 +4658,30 @@
         <v>8</v>
       </c>
     </row>
+    <row r="105">
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>Cap on the LTV horizon (months)</t>
+        </is>
+      </c>
+      <c r="C105" s="115" t="n">
+        <v>36</v>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
+        <is>
+          <t>At 18% annual churn the implied average customer life is 61 months. Valuing five years of an unproven subscription is not credible, so lifetime value is capped at this horizon.</t>
+        </is>
+      </c>
+    </row>
     <row r="106">
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B106" s="116" t="inlineStr">
+        <is>
+          <t>Funding structure: 100% founders' equity — no debt, no grant, no external round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>Equity is injected month by month, only as much as is needed to hold the minimum cash buffer. The total injected is the investment figure on the Dashboard.</t>
         </is>
@@ -4570,7 +4978,7 @@
           <t>Model year</t>
         </is>
       </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="C5" s="92" t="inlineStr">
         <is>
           <t>yr</t>
         </is>
@@ -4822,7 +5230,7 @@
           <t>Months since this market launched</t>
         </is>
       </c>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="C6" s="92" t="inlineStr">
         <is>
           <t>mo</t>
         </is>
@@ -5074,7 +5482,7 @@
           <t>Market year</t>
         </is>
       </c>
-      <c r="C7" s="62" t="inlineStr">
+      <c r="C7" s="92" t="inlineStr">
         <is>
           <t>yr</t>
         </is>
@@ -5393,7 +5801,7 @@
           <t>Opening active customers</t>
         </is>
       </c>
-      <c r="C10" s="62" t="inlineStr">
+      <c r="C10" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -5645,7 +6053,7 @@
           <t>New paying customers</t>
         </is>
       </c>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="C11" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -5897,7 +6305,7 @@
           <t>Customers lost to churn</t>
         </is>
       </c>
-      <c r="C12" s="62" t="inlineStr">
+      <c r="C12" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -6149,7 +6557,7 @@
           <t>Closing active customers</t>
         </is>
       </c>
-      <c r="C13" s="62" t="inlineStr">
+      <c r="C13" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -6401,7 +6809,7 @@
           <t>Average active customers</t>
         </is>
       </c>
-      <c r="C14" s="62" t="inlineStr">
+      <c r="C14" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -6653,7 +7061,7 @@
           <t>Free trials started</t>
         </is>
       </c>
-      <c r="C15" s="62" t="inlineStr">
+      <c r="C15" s="92" t="inlineStr">
         <is>
           <t>trials</t>
         </is>
@@ -6972,7 +7380,7 @@
           <t>Voice Care price (indexed)</t>
         </is>
       </c>
-      <c r="C18" s="62" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -7224,7 +7632,7 @@
           <t>Preventive Care price (indexed)</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="C19" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -7476,7 +7884,7 @@
           <t>Preventive Care attach rate</t>
         </is>
       </c>
-      <c r="C20" s="62" t="inlineStr">
+      <c r="C20" s="92" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -7728,7 +8136,7 @@
           <t xml:space="preserve">   Gross billings — Voice Care</t>
         </is>
       </c>
-      <c r="C21" s="62" t="inlineStr">
+      <c r="C21" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -7980,7 +8388,7 @@
           <t xml:space="preserve">   Gross billings — Preventive Care</t>
         </is>
       </c>
-      <c r="C22" s="62" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -8232,7 +8640,7 @@
           <t>Total gross billings (what customers pay)</t>
         </is>
       </c>
-      <c r="C23" s="62" t="inlineStr">
+      <c r="C23" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -8484,7 +8892,7 @@
           <t xml:space="preserve">   Net revenue — Voice Care</t>
         </is>
       </c>
-      <c r="C24" s="62" t="inlineStr">
+      <c r="C24" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -8736,7 +9144,7 @@
           <t xml:space="preserve">   Net revenue — Preventive Care</t>
         </is>
       </c>
-      <c r="C25" s="62" t="inlineStr">
+      <c r="C25" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -8988,7 +9396,7 @@
           <t>Total net revenue</t>
         </is>
       </c>
-      <c r="C26" s="70" t="inlineStr">
+      <c r="C26" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -9307,7 +9715,7 @@
           <t>Cost per voice minute</t>
         </is>
       </c>
-      <c r="C29" s="62" t="inlineStr">
+      <c r="C29" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -9559,7 +9967,7 @@
           <t xml:space="preserve">   AI voice — paying customers</t>
         </is>
       </c>
-      <c r="C30" s="62" t="inlineStr">
+      <c r="C30" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -9811,7 +10219,7 @@
           <t xml:space="preserve">   AI voice — free trials</t>
         </is>
       </c>
-      <c r="C31" s="62" t="inlineStr">
+      <c r="C31" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -10063,7 +10471,7 @@
           <t xml:space="preserve">   Data &amp; storage</t>
         </is>
       </c>
-      <c r="C32" s="62" t="inlineStr">
+      <c r="C32" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -10315,7 +10723,7 @@
           <t xml:space="preserve">   Preventive Care variable cost</t>
         </is>
       </c>
-      <c r="C33" s="62" t="inlineStr">
+      <c r="C33" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -10567,7 +10975,7 @@
           <t>Total cost of service</t>
         </is>
       </c>
-      <c r="C34" s="62" t="inlineStr">
+      <c r="C34" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -10819,7 +11227,7 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C35" s="70" t="inlineStr">
+      <c r="C35" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -11071,7 +11479,7 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C36" s="62" t="inlineStr">
+      <c r="C36" s="92" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -11390,7 +11798,7 @@
           <t>Cost per acquired customer</t>
         </is>
       </c>
-      <c r="C39" s="62" t="inlineStr">
+      <c r="C39" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -11642,7 +12050,7 @@
           <t>Acquisition spend</t>
         </is>
       </c>
-      <c r="C40" s="62" t="inlineStr">
+      <c r="C40" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -11894,7 +12302,7 @@
           <t>Contribution after acquisition</t>
         </is>
       </c>
-      <c r="C41" s="70" t="inlineStr">
+      <c r="C41" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -12431,7 +12839,7 @@
           <t>Model year</t>
         </is>
       </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="C5" s="92" t="inlineStr">
         <is>
           <t>yr</t>
         </is>
@@ -12683,7 +13091,7 @@
           <t>Months since this market launched</t>
         </is>
       </c>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="C6" s="92" t="inlineStr">
         <is>
           <t>mo</t>
         </is>
@@ -12935,7 +13343,7 @@
           <t>Market year</t>
         </is>
       </c>
-      <c r="C7" s="62" t="inlineStr">
+      <c r="C7" s="92" t="inlineStr">
         <is>
           <t>yr</t>
         </is>
@@ -13254,7 +13662,7 @@
           <t>Opening active customers</t>
         </is>
       </c>
-      <c r="C10" s="62" t="inlineStr">
+      <c r="C10" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -13506,7 +13914,7 @@
           <t>New paying customers</t>
         </is>
       </c>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="C11" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -13758,7 +14166,7 @@
           <t>Customers lost to churn</t>
         </is>
       </c>
-      <c r="C12" s="62" t="inlineStr">
+      <c r="C12" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -14010,7 +14418,7 @@
           <t>Closing active customers</t>
         </is>
       </c>
-      <c r="C13" s="62" t="inlineStr">
+      <c r="C13" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -14262,7 +14670,7 @@
           <t>Average active customers</t>
         </is>
       </c>
-      <c r="C14" s="62" t="inlineStr">
+      <c r="C14" s="92" t="inlineStr">
         <is>
           <t>cust</t>
         </is>
@@ -14514,7 +14922,7 @@
           <t>Free trials started</t>
         </is>
       </c>
-      <c r="C15" s="62" t="inlineStr">
+      <c r="C15" s="92" t="inlineStr">
         <is>
           <t>trials</t>
         </is>
@@ -14833,7 +15241,7 @@
           <t>Voice Care price (indexed)</t>
         </is>
       </c>
-      <c r="C18" s="62" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -15085,7 +15493,7 @@
           <t>Preventive Care price (indexed)</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="C19" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -15337,7 +15745,7 @@
           <t>Preventive Care attach rate</t>
         </is>
       </c>
-      <c r="C20" s="62" t="inlineStr">
+      <c r="C20" s="92" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -15589,7 +15997,7 @@
           <t xml:space="preserve">   Gross billings — Voice Care</t>
         </is>
       </c>
-      <c r="C21" s="62" t="inlineStr">
+      <c r="C21" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -15841,7 +16249,7 @@
           <t xml:space="preserve">   Gross billings — Preventive Care</t>
         </is>
       </c>
-      <c r="C22" s="62" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -16093,7 +16501,7 @@
           <t>Total gross billings (what customers pay)</t>
         </is>
       </c>
-      <c r="C23" s="62" t="inlineStr">
+      <c r="C23" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -16345,7 +16753,7 @@
           <t xml:space="preserve">   Net revenue — Voice Care</t>
         </is>
       </c>
-      <c r="C24" s="62" t="inlineStr">
+      <c r="C24" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -16597,7 +17005,7 @@
           <t xml:space="preserve">   Net revenue — Preventive Care</t>
         </is>
       </c>
-      <c r="C25" s="62" t="inlineStr">
+      <c r="C25" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -16849,7 +17257,7 @@
           <t>Total net revenue</t>
         </is>
       </c>
-      <c r="C26" s="70" t="inlineStr">
+      <c r="C26" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -17168,7 +17576,7 @@
           <t>Cost per voice minute</t>
         </is>
       </c>
-      <c r="C29" s="62" t="inlineStr">
+      <c r="C29" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -17420,7 +17828,7 @@
           <t xml:space="preserve">   AI voice — paying customers</t>
         </is>
       </c>
-      <c r="C30" s="62" t="inlineStr">
+      <c r="C30" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -17672,7 +18080,7 @@
           <t xml:space="preserve">   AI voice — free trials</t>
         </is>
       </c>
-      <c r="C31" s="62" t="inlineStr">
+      <c r="C31" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -17924,7 +18332,7 @@
           <t xml:space="preserve">   Data &amp; storage</t>
         </is>
       </c>
-      <c r="C32" s="62" t="inlineStr">
+      <c r="C32" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -18176,7 +18584,7 @@
           <t xml:space="preserve">   Preventive Care variable cost</t>
         </is>
       </c>
-      <c r="C33" s="62" t="inlineStr">
+      <c r="C33" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -18428,7 +18836,7 @@
           <t>Total cost of service</t>
         </is>
       </c>
-      <c r="C34" s="62" t="inlineStr">
+      <c r="C34" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -18680,7 +19088,7 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C35" s="70" t="inlineStr">
+      <c r="C35" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -18932,7 +19340,7 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C36" s="62" t="inlineStr">
+      <c r="C36" s="92" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -19251,7 +19659,7 @@
           <t>Cost per acquired customer</t>
         </is>
       </c>
-      <c r="C39" s="62" t="inlineStr">
+      <c r="C39" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -19503,7 +19911,7 @@
           <t>Acquisition spend</t>
         </is>
       </c>
-      <c r="C40" s="62" t="inlineStr">
+      <c r="C40" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -19755,7 +20163,7 @@
           <t>Contribution after acquisition</t>
         </is>
       </c>
-      <c r="C41" s="70" t="inlineStr">
+      <c r="C41" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -20292,7 +20700,7 @@
           <t>Model year</t>
         </is>
       </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="C5" s="92" t="inlineStr">
         <is>
           <t>yr</t>
         </is>
@@ -20611,7 +21019,7 @@
           <t xml:space="preserve">    Net revenue — Portugal</t>
         </is>
       </c>
-      <c r="C8" s="62" t="inlineStr">
+      <c r="C8" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -20863,7 +21271,7 @@
           <t xml:space="preserve">    Net revenue — Spain</t>
         </is>
       </c>
-      <c r="C9" s="62" t="inlineStr">
+      <c r="C9" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -21115,7 +21523,7 @@
           <t>Total net revenue</t>
         </is>
       </c>
-      <c r="C10" s="70" t="inlineStr">
+      <c r="C10" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -21367,7 +21775,7 @@
           <t xml:space="preserve">    Cost of service — Portugal</t>
         </is>
       </c>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="C11" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -21619,7 +22027,7 @@
           <t xml:space="preserve">    Cost of service — Spain</t>
         </is>
       </c>
-      <c r="C12" s="62" t="inlineStr">
+      <c r="C12" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -21871,7 +22279,7 @@
           <t>Total cost of service</t>
         </is>
       </c>
-      <c r="C13" s="62" t="inlineStr">
+      <c r="C13" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -22123,7 +22531,7 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="C14" s="70" t="inlineStr">
+      <c r="C14" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -22375,7 +22783,7 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="C15" s="62" t="inlineStr">
+      <c r="C15" s="92" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -22627,7 +23035,7 @@
           <t xml:space="preserve">    Customer acquisition (COCA)</t>
         </is>
       </c>
-      <c r="C17" s="62" t="inlineStr">
+      <c r="C17" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -22879,7 +23287,7 @@
           <t xml:space="preserve">    Brand marketing &amp; content</t>
         </is>
       </c>
-      <c r="C18" s="62" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -23131,7 +23539,7 @@
           <t xml:space="preserve">    Personnel</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="C19" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -23383,7 +23791,7 @@
           <t xml:space="preserve">    Cloud &amp; tools</t>
         </is>
       </c>
-      <c r="C20" s="62" t="inlineStr">
+      <c r="C20" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -23635,7 +24043,7 @@
           <t xml:space="preserve">    General &amp; administrative</t>
         </is>
       </c>
-      <c r="C21" s="62" t="inlineStr">
+      <c r="C21" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -23887,7 +24295,7 @@
           <t>Total operating expenses</t>
         </is>
       </c>
-      <c r="C22" s="62" t="inlineStr">
+      <c r="C22" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -24139,7 +24547,7 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C23" s="70" t="inlineStr">
+      <c r="C23" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -24391,7 +24799,7 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="C24" s="62" t="inlineStr">
+      <c r="C24" s="92" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -24643,7 +25051,7 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="C25" s="62" t="inlineStr">
+      <c r="C25" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -24895,7 +25303,7 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C26" s="62" t="inlineStr">
+      <c r="C26" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -25147,7 +25555,7 @@
           <t>Tax loss pool — opening</t>
         </is>
       </c>
-      <c r="C27" s="62" t="inlineStr">
+      <c r="C27" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -25399,7 +25807,7 @@
           <t>Corporation tax</t>
         </is>
       </c>
-      <c r="C28" s="62" t="inlineStr">
+      <c r="C28" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -25651,7 +26059,7 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="C29" s="70" t="inlineStr">
+      <c r="C29" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -25903,7 +26311,7 @@
           <t>Tax loss pool — closing</t>
         </is>
       </c>
-      <c r="C30" s="62" t="inlineStr">
+      <c r="C30" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -26222,7 +26630,7 @@
           <t xml:space="preserve">    Voice Care platform build</t>
         </is>
       </c>
-      <c r="C33" s="62" t="inlineStr">
+      <c r="C33" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -26474,7 +26882,7 @@
           <t xml:space="preserve">    Preventive Care module</t>
         </is>
       </c>
-      <c r="C34" s="62" t="inlineStr">
+      <c r="C34" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -26726,7 +27134,7 @@
           <t xml:space="preserve">    Spain localisation &amp; compliance</t>
         </is>
       </c>
-      <c r="C35" s="62" t="inlineStr">
+      <c r="C35" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -26978,7 +27386,7 @@
           <t xml:space="preserve">    Ongoing development capex</t>
         </is>
       </c>
-      <c r="C36" s="62" t="inlineStr">
+      <c r="C36" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -27230,7 +27638,7 @@
           <t>Total capital expenditure</t>
         </is>
       </c>
-      <c r="C37" s="62" t="inlineStr">
+      <c r="C37" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -27482,7 +27890,7 @@
           <t>Cumulative capital expenditure</t>
         </is>
       </c>
-      <c r="C38" s="62" t="inlineStr">
+      <c r="C38" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -27734,7 +28142,7 @@
           <t>Gross fixed assets</t>
         </is>
       </c>
-      <c r="C40" s="62" t="inlineStr">
+      <c r="C40" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -27986,7 +28394,7 @@
           <t>Accumulated depreciation</t>
         </is>
       </c>
-      <c r="C41" s="62" t="inlineStr">
+      <c r="C41" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -28238,7 +28646,7 @@
           <t>Depreciation charge for the month</t>
         </is>
       </c>
-      <c r="C42" s="62" t="inlineStr">
+      <c r="C42" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -28490,7 +28898,7 @@
           <t>Net fixed assets</t>
         </is>
       </c>
-      <c r="C43" s="62" t="inlineStr">
+      <c r="C43" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -28809,7 +29217,7 @@
           <t xml:space="preserve">    Net revenue per active customer</t>
         </is>
       </c>
-      <c r="C46" s="62" t="inlineStr">
+      <c r="C46" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -29061,7 +29469,7 @@
           <t xml:space="preserve">    Annual-prepay cash collected up front</t>
         </is>
       </c>
-      <c r="C47" s="62" t="inlineStr">
+      <c r="C47" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -29313,7 +29721,7 @@
           <t xml:space="preserve">    Receivables</t>
         </is>
       </c>
-      <c r="C48" s="62" t="inlineStr">
+      <c r="C48" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -29565,7 +29973,7 @@
           <t xml:space="preserve">    Payables</t>
         </is>
       </c>
-      <c r="C49" s="62" t="inlineStr">
+      <c r="C49" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -29817,7 +30225,7 @@
           <t xml:space="preserve">    Deferred revenue (annual prepay)</t>
         </is>
       </c>
-      <c r="C50" s="62" t="inlineStr">
+      <c r="C50" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -30069,7 +30477,7 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="C51" s="62" t="inlineStr">
+      <c r="C51" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -30321,7 +30729,7 @@
           <t>Change in net working capital</t>
         </is>
       </c>
-      <c r="C52" s="62" t="inlineStr">
+      <c r="C52" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -30640,7 +31048,7 @@
           <t xml:space="preserve">    EBITDA</t>
         </is>
       </c>
-      <c r="C55" s="62" t="inlineStr">
+      <c r="C55" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -30892,7 +31300,7 @@
           <t xml:space="preserve">    Corporation tax paid</t>
         </is>
       </c>
-      <c r="C56" s="62" t="inlineStr">
+      <c r="C56" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -31144,7 +31552,7 @@
           <t xml:space="preserve">    Capital expenditure</t>
         </is>
       </c>
-      <c r="C57" s="62" t="inlineStr">
+      <c r="C57" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -31396,7 +31804,7 @@
           <t xml:space="preserve">    Change in working capital</t>
         </is>
       </c>
-      <c r="C58" s="62" t="inlineStr">
+      <c r="C58" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -31648,7 +32056,7 @@
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C59" s="70" t="inlineStr">
+      <c r="C59" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -31900,7 +32308,7 @@
           <t>Cumulative free cash flow</t>
         </is>
       </c>
-      <c r="C60" s="62" t="inlineStr">
+      <c r="C60" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -32152,7 +32560,7 @@
           <t>Cash before founders' injection</t>
         </is>
       </c>
-      <c r="C61" s="62" t="inlineStr">
+      <c r="C61" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -32404,7 +32812,7 @@
           <t>Founders' equity injected</t>
         </is>
       </c>
-      <c r="C62" s="75" t="inlineStr">
+      <c r="C62" s="108" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -32656,7 +33064,7 @@
           <t>Cumulative equity invested</t>
         </is>
       </c>
-      <c r="C63" s="62" t="inlineStr">
+      <c r="C63" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -32908,7 +33316,7 @@
           <t>Cash — closing balance</t>
         </is>
       </c>
-      <c r="C64" s="70" t="inlineStr">
+      <c r="C64" s="98" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -33227,7 +33635,7 @@
           <t xml:space="preserve">    Cash</t>
         </is>
       </c>
-      <c r="C67" s="62" t="inlineStr">
+      <c r="C67" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -33479,7 +33887,7 @@
           <t xml:space="preserve">    Receivables</t>
         </is>
       </c>
-      <c r="C68" s="62" t="inlineStr">
+      <c r="C68" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -33731,7 +34139,7 @@
           <t xml:space="preserve">    Net fixed assets</t>
         </is>
       </c>
-      <c r="C69" s="62" t="inlineStr">
+      <c r="C69" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -33983,7 +34391,7 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C70" s="62" t="inlineStr">
+      <c r="C70" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -34235,7 +34643,7 @@
           <t xml:space="preserve">    Payables</t>
         </is>
       </c>
-      <c r="C71" s="62" t="inlineStr">
+      <c r="C71" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -34487,7 +34895,7 @@
           <t xml:space="preserve">    Deferred revenue</t>
         </is>
       </c>
-      <c r="C72" s="62" t="inlineStr">
+      <c r="C72" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -34739,7 +35147,7 @@
           <t xml:space="preserve">    Paid-in equity</t>
         </is>
       </c>
-      <c r="C73" s="62" t="inlineStr">
+      <c r="C73" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -34991,7 +35399,7 @@
           <t xml:space="preserve">    Retained earnings</t>
         </is>
       </c>
-      <c r="C74" s="62" t="inlineStr">
+      <c r="C74" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -35243,7 +35651,7 @@
           <t>Total liabilities &amp; equity</t>
         </is>
       </c>
-      <c r="C75" s="62" t="inlineStr">
+      <c r="C75" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
@@ -35495,7 +35903,7 @@
           <t>Balance check (must be nil)</t>
         </is>
       </c>
-      <c r="C76" s="62" t="inlineStr">
+      <c r="C76" s="92" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
